--- a/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
+++ b/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -676,37 +676,37 @@
         <v>11</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>31</v>
       </c>
       <c r="M2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="n">
+      <c r="P2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>23</v>
-      </c>
       <c r="R2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0</v>
@@ -785,22 +785,22 @@
         <v>2</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="G4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>21</v>
@@ -837,49 +837,49 @@
         <v>3</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="U4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>7</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -968,25 +968,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1092,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>1</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
+++ b/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
@@ -658,16 +658,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2</v>
@@ -676,10 +676,10 @@
         <v>11</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>31</v>
@@ -697,13 +697,13 @@
         <v>31</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>0</v>
@@ -791,7 +791,7 @@
         <v>28</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>26</v>
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>12</v>
@@ -864,13 +864,13 @@
         <v>10</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>3</v>
@@ -898,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>3</v>
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>2</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>0</v>
@@ -1132,16 +1132,16 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>

--- a/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
+++ b/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>

--- a/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
+++ b/Figure_Plot/figure_plot_4_c/output/P_ESS_state_hourly_counts_May2025.xlsx
@@ -658,25 +658,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>31</v>
@@ -688,25 +688,25 @@
         <v>31</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="3" t="n">
         <v>31</v>
       </c>
       <c r="Q2" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R2" s="3" t="n">
-        <v>24</v>
-      </c>
       <c r="S2" s="3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -734,19 +734,19 @@
         <v>27</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>9</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>10</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>4</v>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>28</v>
@@ -810,28 +810,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>14</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>3</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>3</v>
@@ -879,7 +879,7 @@
         <v>2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -901,19 +901,19 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
@@ -968,67 +968,67 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>2</v>
@@ -1059,49 +1059,49 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0</v>
@@ -1132,49 +1132,49 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0</v>
